--- a/innings_blank.xlsx
+++ b/innings_blank.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jayb1/Development/innings-heatmap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7380809-3AB9-CD47-BD0C-6896D6B76D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C11BB086-10B1-3D44-8418-2B5867BF4329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5700" yWindow="2420" windowWidth="27640" windowHeight="16680" xr2:uid="{4D38DE9E-45CF-F446-BA79-BBA4AB2BECC6}"/>
+    <workbookView xWindow="2200" yWindow="1560" windowWidth="27640" windowHeight="16680" xr2:uid="{4D38DE9E-45CF-F446-BA79-BBA4AB2BECC6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$DO$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$DN$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="164">
   <si>
     <t>Baltimore Orioles</t>
   </si>
@@ -425,9 +425,6 @@
     <t>1D1D1D</t>
   </si>
   <si>
-    <t>003831</t>
-  </si>
-  <si>
     <t>D50032</t>
   </si>
   <si>
@@ -536,17 +533,23 @@
     <t>D84E25</t>
   </si>
   <si>
-    <t>html</t>
+    <t>EFB21E</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -909,7 +912,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B84222C-1BCC-384D-8895-C6CB4408DECD}">
-  <dimension ref="A1:DK91"/>
+  <dimension ref="A1:DJ91"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="5.1640625" bestFit="1" customWidth="1"/>
@@ -917,22 +920,22 @@
     <col min="4" max="4" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" style="1" customWidth="1"/>
     <col min="6" max="6" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="19" width="2.1640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="31" width="3.1640625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="3" bestFit="1" customWidth="1"/>
-    <col min="33" max="43" width="3.1640625" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="2.1640625" bestFit="1" customWidth="1"/>
-    <col min="45" max="53" width="3.1640625" bestFit="1" customWidth="1"/>
-    <col min="54" max="77" width="4.1640625" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="3" bestFit="1" customWidth="1"/>
-    <col min="79" max="87" width="4.83203125" bestFit="1" customWidth="1"/>
-    <col min="88" max="111" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="112" max="113" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="114" max="114" width="8" bestFit="1" customWidth="1"/>
-    <col min="115" max="115" width="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="18" width="2.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="30" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="3" bestFit="1" customWidth="1"/>
+    <col min="32" max="42" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="2.1640625" bestFit="1" customWidth="1"/>
+    <col min="44" max="52" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="53" max="76" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="3" bestFit="1" customWidth="1"/>
+    <col min="78" max="86" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="87" max="110" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="111" max="112" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="113" max="113" width="8" bestFit="1" customWidth="1"/>
+    <col min="114" max="114" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>56</v>
       </c>
@@ -960,360 +963,357 @@
       <c r="I1" t="s">
         <v>55</v>
       </c>
-      <c r="J1" t="s">
-        <v>164</v>
+      <c r="J1">
+        <v>1</v>
       </c>
       <c r="K1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="U1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="W1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AC1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AD1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM1">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AN1">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AO1">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AP1">
-        <v>32</v>
-      </c>
-      <c r="AQ1">
         <v>33</v>
       </c>
+      <c r="AQ1" t="s">
+        <v>38</v>
+      </c>
       <c r="AR1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AS1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AT1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AV1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AW1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AX1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AY1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AZ1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="BA1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="BB1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="BC1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="BD1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="BE1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="BF1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="BG1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="BH1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="BI1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="BJ1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="BK1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="BL1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="BM1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="BN1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="BO1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="BP1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="BQ1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="BR1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="BS1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BT1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BU1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BV1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BW1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BX1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BY1" t="s">
-        <v>80</v>
-      </c>
-      <c r="BZ1" t="s">
         <v>48</v>
       </c>
+      <c r="BZ1" t="str">
+        <f>_xlfn.CONCAT(J1,"avg")</f>
+        <v>1avg</v>
+      </c>
       <c r="CA1" t="str">
-        <f>_xlfn.CONCAT(K1,"avg")</f>
-        <v>1avg</v>
+        <f t="shared" ref="CA1:CV1" si="0">_xlfn.CONCAT(K1,"avg")</f>
+        <v>2avg</v>
       </c>
       <c r="CB1" t="str">
-        <f t="shared" ref="CB1:CW1" si="0">_xlfn.CONCAT(L1,"avg")</f>
-        <v>2avg</v>
+        <f t="shared" si="0"/>
+        <v>3avg</v>
       </c>
       <c r="CC1" t="str">
         <f t="shared" si="0"/>
-        <v>3avg</v>
+        <v>4avg</v>
       </c>
       <c r="CD1" t="str">
         <f t="shared" si="0"/>
-        <v>4avg</v>
+        <v>5avg</v>
       </c>
       <c r="CE1" t="str">
         <f t="shared" si="0"/>
-        <v>5avg</v>
+        <v>6avg</v>
       </c>
       <c r="CF1" t="str">
         <f t="shared" si="0"/>
-        <v>6avg</v>
+        <v>7avg</v>
       </c>
       <c r="CG1" t="str">
         <f t="shared" si="0"/>
-        <v>7avg</v>
+        <v>8avg</v>
       </c>
       <c r="CH1" t="str">
         <f t="shared" si="0"/>
-        <v>8avg</v>
+        <v>9avg</v>
       </c>
       <c r="CI1" t="str">
         <f t="shared" si="0"/>
-        <v>9avg</v>
+        <v>10avg</v>
       </c>
       <c r="CJ1" t="str">
         <f t="shared" si="0"/>
-        <v>10avg</v>
+        <v>11avg</v>
       </c>
       <c r="CK1" t="str">
         <f t="shared" si="0"/>
-        <v>11avg</v>
+        <v>12avg</v>
       </c>
       <c r="CL1" t="str">
         <f t="shared" si="0"/>
-        <v>12avg</v>
+        <v>13avg</v>
       </c>
       <c r="CM1" t="str">
         <f t="shared" si="0"/>
-        <v>13avg</v>
+        <v>14avg</v>
       </c>
       <c r="CN1" t="str">
         <f t="shared" si="0"/>
-        <v>14avg</v>
+        <v>15avg</v>
       </c>
       <c r="CO1" t="str">
         <f t="shared" si="0"/>
-        <v>15avg</v>
+        <v>16avg</v>
       </c>
       <c r="CP1" t="str">
         <f t="shared" si="0"/>
-        <v>16avg</v>
+        <v>17avg</v>
       </c>
       <c r="CQ1" t="str">
         <f t="shared" si="0"/>
-        <v>17avg</v>
+        <v>18avg</v>
       </c>
       <c r="CR1" t="str">
         <f t="shared" si="0"/>
-        <v>18avg</v>
+        <v>19avg</v>
       </c>
       <c r="CS1" t="str">
         <f t="shared" si="0"/>
-        <v>19avg</v>
+        <v>20avg</v>
       </c>
       <c r="CT1" t="str">
         <f t="shared" si="0"/>
-        <v>20avg</v>
+        <v>21avg</v>
       </c>
       <c r="CU1" t="str">
         <f t="shared" si="0"/>
-        <v>21avg</v>
+        <v>22avg</v>
       </c>
       <c r="CV1" t="str">
         <f t="shared" si="0"/>
-        <v>22avg</v>
+        <v>23avg</v>
       </c>
       <c r="CW1" t="str">
-        <f t="shared" si="0"/>
-        <v>23avg</v>
+        <f>_xlfn.CONCAT(AG1,"avg")</f>
+        <v>24avg</v>
       </c>
       <c r="CX1" t="str">
-        <f>_xlfn.CONCAT(AH1,"avg")</f>
-        <v>24avg</v>
+        <f t="shared" ref="CX1" si="1">_xlfn.CONCAT(AH1,"avg")</f>
+        <v>25avg</v>
       </c>
       <c r="CY1" t="str">
-        <f t="shared" ref="CY1" si="1">_xlfn.CONCAT(AI1,"avg")</f>
-        <v>25avg</v>
+        <f t="shared" ref="CY1" si="2">_xlfn.CONCAT(AI1,"avg")</f>
+        <v>26avg</v>
       </c>
       <c r="CZ1" t="str">
-        <f t="shared" ref="CZ1" si="2">_xlfn.CONCAT(AJ1,"avg")</f>
-        <v>26avg</v>
+        <f t="shared" ref="CZ1" si="3">_xlfn.CONCAT(AJ1,"avg")</f>
+        <v>27avg</v>
       </c>
       <c r="DA1" t="str">
-        <f t="shared" ref="DA1" si="3">_xlfn.CONCAT(AK1,"avg")</f>
-        <v>27avg</v>
+        <f t="shared" ref="DA1" si="4">_xlfn.CONCAT(AK1,"avg")</f>
+        <v>28avg</v>
       </c>
       <c r="DB1" t="str">
-        <f t="shared" ref="DB1" si="4">_xlfn.CONCAT(AL1,"avg")</f>
-        <v>28avg</v>
+        <f t="shared" ref="DB1" si="5">_xlfn.CONCAT(AL1,"avg")</f>
+        <v>29avg</v>
       </c>
       <c r="DC1" t="str">
-        <f t="shared" ref="DC1" si="5">_xlfn.CONCAT(AM1,"avg")</f>
-        <v>29avg</v>
+        <f t="shared" ref="DC1" si="6">_xlfn.CONCAT(AM1,"avg")</f>
+        <v>30avg</v>
       </c>
       <c r="DD1" t="str">
-        <f t="shared" ref="DD1" si="6">_xlfn.CONCAT(AN1,"avg")</f>
-        <v>30avg</v>
+        <f t="shared" ref="DD1" si="7">_xlfn.CONCAT(AN1,"avg")</f>
+        <v>31avg</v>
       </c>
       <c r="DE1" t="str">
-        <f t="shared" ref="DE1" si="7">_xlfn.CONCAT(AO1,"avg")</f>
-        <v>31avg</v>
+        <f t="shared" ref="DE1" si="8">_xlfn.CONCAT(AO1,"avg")</f>
+        <v>32avg</v>
       </c>
       <c r="DF1" t="str">
-        <f t="shared" ref="DF1" si="8">_xlfn.CONCAT(AP1,"avg")</f>
-        <v>32avg</v>
+        <f t="shared" ref="DF1" si="9">_xlfn.CONCAT(AP1,"avg")</f>
+        <v>33avg</v>
       </c>
       <c r="DG1" t="str">
-        <f t="shared" ref="DG1" si="9">_xlfn.CONCAT(AQ1,"avg")</f>
-        <v>33avg</v>
-      </c>
-      <c r="DH1" t="str">
-        <f t="shared" ref="DH1" si="10">_xlfn.CONCAT(AR1,"avg")</f>
+        <f t="shared" ref="DG1" si="10">_xlfn.CONCAT(AQ1,"avg")</f>
         <v>xavg</v>
       </c>
+      <c r="DH1" t="s">
+        <v>49</v>
+      </c>
       <c r="DI1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="DJ1" t="s">
-        <v>50</v>
-      </c>
-      <c r="DK1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>110</v>
       </c>
@@ -1341,6 +1341,9 @@
       <c r="I2" t="s">
         <v>33</v>
       </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
       <c r="K2">
         <v>0</v>
       </c>
@@ -1653,11 +1656,8 @@
       <c r="DJ2">
         <v>0</v>
       </c>
-      <c r="DK2">
-        <v>0</v>
-      </c>
     </row>
-    <row r="3" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>110</v>
       </c>
@@ -1685,6 +1685,9 @@
       <c r="I3" t="s">
         <v>33</v>
       </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
       <c r="K3">
         <v>0</v>
       </c>
@@ -1997,11 +2000,8 @@
       <c r="DJ3">
         <v>0</v>
       </c>
-      <c r="DK3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="4" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>110</v>
       </c>
@@ -2029,6 +2029,9 @@
       <c r="I4" t="s">
         <v>33</v>
       </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
       <c r="K4">
         <v>0</v>
       </c>
@@ -2341,11 +2344,8 @@
       <c r="DJ4">
         <v>0</v>
       </c>
-      <c r="DK4">
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>111</v>
       </c>
@@ -2373,6 +2373,9 @@
       <c r="I5" t="s">
         <v>33</v>
       </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
       <c r="K5">
         <v>0</v>
       </c>
@@ -2685,11 +2688,8 @@
       <c r="DJ5">
         <v>0</v>
       </c>
-      <c r="DK5">
-        <v>0</v>
-      </c>
     </row>
-    <row r="6" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>111</v>
       </c>
@@ -2717,6 +2717,9 @@
       <c r="I6" t="s">
         <v>33</v>
       </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
       <c r="K6">
         <v>0</v>
       </c>
@@ -3029,11 +3032,8 @@
       <c r="DJ6">
         <v>0</v>
       </c>
-      <c r="DK6">
-        <v>0</v>
-      </c>
     </row>
-    <row r="7" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>111</v>
       </c>
@@ -3061,6 +3061,9 @@
       <c r="I7" t="s">
         <v>33</v>
       </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
       <c r="K7">
         <v>0</v>
       </c>
@@ -3373,11 +3376,8 @@
       <c r="DJ7">
         <v>0</v>
       </c>
-      <c r="DK7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="8" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>147</v>
       </c>
@@ -3385,7 +3385,7 @@
         <v>84</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>118</v>
@@ -3402,6 +3402,9 @@
       <c r="I8" t="s">
         <v>33</v>
       </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
       <c r="K8">
         <v>0</v>
       </c>
@@ -3714,11 +3717,8 @@
       <c r="DJ8">
         <v>0</v>
       </c>
-      <c r="DK8">
-        <v>0</v>
-      </c>
     </row>
-    <row r="9" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>147</v>
       </c>
@@ -3726,7 +3726,7 @@
         <v>84</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>118</v>
@@ -3743,6 +3743,9 @@
       <c r="I9" t="s">
         <v>33</v>
       </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
       <c r="K9">
         <v>0</v>
       </c>
@@ -4055,11 +4058,8 @@
       <c r="DJ9">
         <v>0</v>
       </c>
-      <c r="DK9">
-        <v>0</v>
-      </c>
     </row>
-    <row r="10" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>147</v>
       </c>
@@ -4067,7 +4067,7 @@
         <v>84</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>118</v>
@@ -4084,6 +4084,9 @@
       <c r="I10" t="s">
         <v>33</v>
       </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
       <c r="K10">
         <v>0</v>
       </c>
@@ -4396,11 +4399,8 @@
       <c r="DJ10">
         <v>0</v>
       </c>
-      <c r="DK10">
-        <v>0</v>
-      </c>
     </row>
-    <row r="11" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>139</v>
       </c>
@@ -4408,13 +4408,13 @@
         <v>85</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>118</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F11" t="s">
         <v>3</v>
@@ -4428,6 +4428,9 @@
       <c r="I11" t="s">
         <v>33</v>
       </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
       <c r="K11">
         <v>0</v>
       </c>
@@ -4740,11 +4743,8 @@
       <c r="DJ11">
         <v>0</v>
       </c>
-      <c r="DK11">
-        <v>0</v>
-      </c>
     </row>
-    <row r="12" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>139</v>
       </c>
@@ -4752,13 +4752,13 @@
         <v>85</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>118</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F12" t="s">
         <v>3</v>
@@ -4772,6 +4772,9 @@
       <c r="I12" t="s">
         <v>33</v>
       </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
       <c r="K12">
         <v>0</v>
       </c>
@@ -5084,11 +5087,8 @@
       <c r="DJ12">
         <v>0</v>
       </c>
-      <c r="DK12">
-        <v>0</v>
-      </c>
     </row>
-    <row r="13" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>139</v>
       </c>
@@ -5096,13 +5096,13 @@
         <v>85</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>118</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F13" t="s">
         <v>3</v>
@@ -5116,6 +5116,9 @@
       <c r="I13" t="s">
         <v>33</v>
       </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
       <c r="K13">
         <v>0</v>
       </c>
@@ -5428,11 +5431,8 @@
       <c r="DJ13">
         <v>0</v>
       </c>
-      <c r="DK13">
-        <v>0</v>
-      </c>
     </row>
-    <row r="14" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>141</v>
       </c>
@@ -5446,7 +5446,7 @@
         <v>118</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="F14" t="s">
         <v>4</v>
@@ -5460,6 +5460,9 @@
       <c r="I14" t="s">
         <v>33</v>
       </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
       <c r="K14">
         <v>0</v>
       </c>
@@ -5772,11 +5775,8 @@
       <c r="DJ14">
         <v>0</v>
       </c>
-      <c r="DK14">
-        <v>0</v>
-      </c>
     </row>
-    <row r="15" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>141</v>
       </c>
@@ -5790,7 +5790,7 @@
         <v>118</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="F15" t="s">
         <v>4</v>
@@ -5804,6 +5804,9 @@
       <c r="I15" t="s">
         <v>33</v>
       </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
       <c r="K15">
         <v>0</v>
       </c>
@@ -6116,11 +6119,8 @@
       <c r="DJ15">
         <v>0</v>
       </c>
-      <c r="DK15">
-        <v>0</v>
-      </c>
     </row>
-    <row r="16" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>141</v>
       </c>
@@ -6134,7 +6134,7 @@
         <v>118</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="F16" t="s">
         <v>4</v>
@@ -6148,6 +6148,9 @@
       <c r="I16" t="s">
         <v>33</v>
       </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
       <c r="K16">
         <v>0</v>
       </c>
@@ -6460,11 +6463,8 @@
       <c r="DJ16">
         <v>0</v>
       </c>
-      <c r="DK16">
-        <v>0</v>
-      </c>
     </row>
-    <row r="17" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>145</v>
       </c>
@@ -6472,7 +6472,7 @@
         <v>87</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>118</v>
@@ -6489,6 +6489,9 @@
       <c r="I17" t="s">
         <v>34</v>
       </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
       <c r="K17">
         <v>0</v>
       </c>
@@ -6801,11 +6804,8 @@
       <c r="DJ17">
         <v>0</v>
       </c>
-      <c r="DK17">
-        <v>0</v>
-      </c>
     </row>
-    <row r="18" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>145</v>
       </c>
@@ -6813,7 +6813,7 @@
         <v>87</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>118</v>
@@ -6830,6 +6830,9 @@
       <c r="I18" t="s">
         <v>34</v>
       </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
       <c r="K18">
         <v>0</v>
       </c>
@@ -7142,11 +7145,8 @@
       <c r="DJ18">
         <v>0</v>
       </c>
-      <c r="DK18">
-        <v>0</v>
-      </c>
     </row>
-    <row r="19" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>145</v>
       </c>
@@ -7154,7 +7154,7 @@
         <v>87</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>118</v>
@@ -7171,6 +7171,9 @@
       <c r="I19" t="s">
         <v>34</v>
       </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
       <c r="K19">
         <v>0</v>
       </c>
@@ -7483,11 +7486,8 @@
       <c r="DJ19">
         <v>0</v>
       </c>
-      <c r="DK19">
-        <v>0</v>
-      </c>
     </row>
-    <row r="20" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>114</v>
       </c>
@@ -7495,13 +7495,13 @@
         <v>88</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="F20" t="s">
         <v>5</v>
@@ -7515,6 +7515,9 @@
       <c r="I20" t="s">
         <v>34</v>
       </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
       <c r="K20">
         <v>0</v>
       </c>
@@ -7827,11 +7830,8 @@
       <c r="DJ20">
         <v>0</v>
       </c>
-      <c r="DK20">
-        <v>0</v>
-      </c>
     </row>
-    <row r="21" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>114</v>
       </c>
@@ -7839,13 +7839,13 @@
         <v>88</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="F21" t="s">
         <v>5</v>
@@ -7859,6 +7859,9 @@
       <c r="I21" t="s">
         <v>34</v>
       </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
       <c r="K21">
         <v>0</v>
       </c>
@@ -8171,11 +8174,8 @@
       <c r="DJ21">
         <v>0</v>
       </c>
-      <c r="DK21">
-        <v>0</v>
-      </c>
     </row>
-    <row r="22" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>114</v>
       </c>
@@ -8183,13 +8183,13 @@
         <v>88</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="F22" t="s">
         <v>5</v>
@@ -8203,6 +8203,9 @@
       <c r="I22" t="s">
         <v>34</v>
       </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
       <c r="K22">
         <v>0</v>
       </c>
@@ -8515,11 +8518,8 @@
       <c r="DJ22">
         <v>0</v>
       </c>
-      <c r="DK22">
-        <v>0</v>
-      </c>
     </row>
-    <row r="23" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>116</v>
       </c>
@@ -8533,7 +8533,7 @@
         <v>118</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F23" t="s">
         <v>7</v>
@@ -8547,6 +8547,9 @@
       <c r="I23" t="s">
         <v>34</v>
       </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
       <c r="K23">
         <v>0</v>
       </c>
@@ -8859,11 +8862,8 @@
       <c r="DJ23">
         <v>0</v>
       </c>
-      <c r="DK23">
-        <v>0</v>
-      </c>
     </row>
-    <row r="24" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>116</v>
       </c>
@@ -8877,7 +8877,7 @@
         <v>118</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F24" t="s">
         <v>7</v>
@@ -8891,6 +8891,9 @@
       <c r="I24" t="s">
         <v>34</v>
       </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
       <c r="K24">
         <v>0</v>
       </c>
@@ -9203,11 +9206,8 @@
       <c r="DJ24">
         <v>0</v>
       </c>
-      <c r="DK24">
-        <v>0</v>
-      </c>
     </row>
-    <row r="25" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>116</v>
       </c>
@@ -9221,7 +9221,7 @@
         <v>118</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F25" t="s">
         <v>7</v>
@@ -9235,6 +9235,9 @@
       <c r="I25" t="s">
         <v>34</v>
       </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
       <c r="K25">
         <v>0</v>
       </c>
@@ -9547,11 +9550,8 @@
       <c r="DJ25">
         <v>0</v>
       </c>
-      <c r="DK25">
-        <v>0</v>
-      </c>
     </row>
-    <row r="26" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>118</v>
       </c>
@@ -9559,7 +9559,7 @@
         <v>90</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>118</v>
@@ -9576,6 +9576,9 @@
       <c r="I26" t="s">
         <v>34</v>
       </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
       <c r="K26">
         <v>0</v>
       </c>
@@ -9888,11 +9891,8 @@
       <c r="DJ26">
         <v>0</v>
       </c>
-      <c r="DK26">
-        <v>0</v>
-      </c>
     </row>
-    <row r="27" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>118</v>
       </c>
@@ -9900,7 +9900,7 @@
         <v>90</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>118</v>
@@ -9917,6 +9917,9 @@
       <c r="I27" t="s">
         <v>34</v>
       </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
       <c r="K27">
         <v>0</v>
       </c>
@@ -10229,11 +10232,8 @@
       <c r="DJ27">
         <v>0</v>
       </c>
-      <c r="DK27">
-        <v>0</v>
-      </c>
     </row>
-    <row r="28" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>118</v>
       </c>
@@ -10241,7 +10241,7 @@
         <v>90</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>118</v>
@@ -10258,6 +10258,9 @@
       <c r="I28" t="s">
         <v>34</v>
       </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
       <c r="K28">
         <v>0</v>
       </c>
@@ -10570,11 +10573,8 @@
       <c r="DJ28">
         <v>0</v>
       </c>
-      <c r="DK28">
-        <v>0</v>
-      </c>
     </row>
-    <row r="29" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>142</v>
       </c>
@@ -10582,10 +10582,10 @@
         <v>91</v>
       </c>
       <c r="C29" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>153</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>118</v>
@@ -10602,6 +10602,9 @@
       <c r="I29" t="s">
         <v>34</v>
       </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
       <c r="K29">
         <v>0</v>
       </c>
@@ -10914,11 +10917,8 @@
       <c r="DJ29">
         <v>0</v>
       </c>
-      <c r="DK29">
-        <v>0</v>
-      </c>
     </row>
-    <row r="30" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>142</v>
       </c>
@@ -10926,10 +10926,10 @@
         <v>91</v>
       </c>
       <c r="C30" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>153</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>118</v>
@@ -10946,6 +10946,9 @@
       <c r="I30" t="s">
         <v>34</v>
       </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
       <c r="K30">
         <v>0</v>
       </c>
@@ -11258,11 +11261,8 @@
       <c r="DJ30">
         <v>0</v>
       </c>
-      <c r="DK30">
-        <v>0</v>
-      </c>
     </row>
-    <row r="31" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>142</v>
       </c>
@@ -11270,10 +11270,10 @@
         <v>91</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>153</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>118</v>
@@ -11290,6 +11290,9 @@
       <c r="I31" t="s">
         <v>34</v>
       </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
       <c r="K31">
         <v>0</v>
       </c>
@@ -11602,11 +11605,8 @@
       <c r="DJ31">
         <v>0</v>
       </c>
-      <c r="DK31">
-        <v>0</v>
-      </c>
     </row>
-    <row r="32" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>133</v>
       </c>
@@ -11620,7 +11620,7 @@
         <v>118</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>127</v>
+        <v>163</v>
       </c>
       <c r="F32" t="s">
         <v>11</v>
@@ -11634,6 +11634,9 @@
       <c r="I32" t="s">
         <v>35</v>
       </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
       <c r="K32">
         <v>0</v>
       </c>
@@ -11946,11 +11949,8 @@
       <c r="DJ32">
         <v>0</v>
       </c>
-      <c r="DK32">
-        <v>0</v>
-      </c>
     </row>
-    <row r="33" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>133</v>
       </c>
@@ -11964,7 +11964,7 @@
         <v>118</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>127</v>
+        <v>163</v>
       </c>
       <c r="F33" t="s">
         <v>11</v>
@@ -11978,6 +11978,9 @@
       <c r="I33" t="s">
         <v>35</v>
       </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
       <c r="K33">
         <v>0</v>
       </c>
@@ -12290,11 +12293,8 @@
       <c r="DJ33">
         <v>0</v>
       </c>
-      <c r="DK33">
-        <v>0</v>
-      </c>
     </row>
-    <row r="34" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>133</v>
       </c>
@@ -12308,7 +12308,7 @@
         <v>118</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>127</v>
+        <v>163</v>
       </c>
       <c r="F34" t="s">
         <v>11</v>
@@ -12322,6 +12322,9 @@
       <c r="I34" t="s">
         <v>35</v>
       </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
       <c r="K34">
         <v>0</v>
       </c>
@@ -12634,11 +12637,8 @@
       <c r="DJ34">
         <v>0</v>
       </c>
-      <c r="DK34">
-        <v>0</v>
-      </c>
     </row>
-    <row r="35" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>117</v>
       </c>
@@ -12646,13 +12646,13 @@
         <v>93</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>118</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F35" t="s">
         <v>12</v>
@@ -12666,6 +12666,9 @@
       <c r="I35" t="s">
         <v>35</v>
       </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
       <c r="K35">
         <v>0</v>
       </c>
@@ -12978,11 +12981,8 @@
       <c r="DJ35">
         <v>0</v>
       </c>
-      <c r="DK35">
-        <v>0</v>
-      </c>
     </row>
-    <row r="36" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>117</v>
       </c>
@@ -12990,13 +12990,13 @@
         <v>93</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>118</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F36" t="s">
         <v>12</v>
@@ -13010,6 +13010,9 @@
       <c r="I36" t="s">
         <v>35</v>
       </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
       <c r="K36">
         <v>0</v>
       </c>
@@ -13322,11 +13325,8 @@
       <c r="DJ36">
         <v>0</v>
       </c>
-      <c r="DK36">
-        <v>0</v>
-      </c>
     </row>
-    <row r="37" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>117</v>
       </c>
@@ -13334,13 +13334,13 @@
         <v>93</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>118</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F37" t="s">
         <v>12</v>
@@ -13354,6 +13354,9 @@
       <c r="I37" t="s">
         <v>35</v>
       </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
       <c r="K37">
         <v>0</v>
       </c>
@@ -13666,11 +13669,8 @@
       <c r="DJ37">
         <v>0</v>
       </c>
-      <c r="DK37">
-        <v>0</v>
-      </c>
     </row>
-    <row r="38" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>108</v>
       </c>
@@ -13678,13 +13678,13 @@
         <v>94</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D38" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>134</v>
       </c>
       <c r="F38" t="s">
         <v>10</v>
@@ -13698,6 +13698,9 @@
       <c r="I38" t="s">
         <v>35</v>
       </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
       <c r="K38">
         <v>0</v>
       </c>
@@ -14010,11 +14013,8 @@
       <c r="DJ38">
         <v>0</v>
       </c>
-      <c r="DK38">
-        <v>0</v>
-      </c>
     </row>
-    <row r="39" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>108</v>
       </c>
@@ -14022,13 +14022,13 @@
         <v>94</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D39" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>134</v>
       </c>
       <c r="F39" t="s">
         <v>10</v>
@@ -14042,6 +14042,9 @@
       <c r="I39" t="s">
         <v>35</v>
       </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
       <c r="K39">
         <v>0</v>
       </c>
@@ -14354,11 +14357,8 @@
       <c r="DJ39">
         <v>0</v>
       </c>
-      <c r="DK39">
-        <v>0</v>
-      </c>
     </row>
-    <row r="40" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>108</v>
       </c>
@@ -14366,13 +14366,13 @@
         <v>94</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D40" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>134</v>
       </c>
       <c r="F40" t="s">
         <v>10</v>
@@ -14386,6 +14386,9 @@
       <c r="I40" t="s">
         <v>35</v>
       </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
       <c r="K40">
         <v>0</v>
       </c>
@@ -14698,11 +14701,8 @@
       <c r="DJ40">
         <v>0</v>
       </c>
-      <c r="DK40">
-        <v>0</v>
-      </c>
     </row>
-    <row r="41" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>136</v>
       </c>
@@ -14710,13 +14710,13 @@
         <v>95</v>
       </c>
       <c r="C41" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D41" t="s">
+        <v>128</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E41" t="s">
-        <v>129</v>
       </c>
       <c r="F41" t="s">
         <v>13</v>
@@ -14730,6 +14730,9 @@
       <c r="I41" t="s">
         <v>35</v>
       </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
       <c r="K41">
         <v>0</v>
       </c>
@@ -15042,11 +15045,8 @@
       <c r="DJ41">
         <v>0</v>
       </c>
-      <c r="DK41">
-        <v>0</v>
-      </c>
     </row>
-    <row r="42" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>136</v>
       </c>
@@ -15054,13 +15054,13 @@
         <v>95</v>
       </c>
       <c r="C42" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D42" t="s">
+        <v>128</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E42" t="s">
-        <v>129</v>
       </c>
       <c r="F42" t="s">
         <v>13</v>
@@ -15074,6 +15074,9 @@
       <c r="I42" t="s">
         <v>35</v>
       </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
       <c r="K42">
         <v>0</v>
       </c>
@@ -15386,11 +15389,8 @@
       <c r="DJ42">
         <v>0</v>
       </c>
-      <c r="DK42">
-        <v>0</v>
-      </c>
     </row>
-    <row r="43" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>136</v>
       </c>
@@ -15398,13 +15398,13 @@
         <v>95</v>
       </c>
       <c r="C43" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D43" t="s">
+        <v>128</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E43" t="s">
-        <v>129</v>
       </c>
       <c r="F43" t="s">
         <v>13</v>
@@ -15418,6 +15418,9 @@
       <c r="I43" t="s">
         <v>35</v>
       </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
       <c r="K43">
         <v>0</v>
       </c>
@@ -15730,11 +15733,8 @@
       <c r="DJ43">
         <v>0</v>
       </c>
-      <c r="DK43">
-        <v>0</v>
-      </c>
     </row>
-    <row r="44" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>140</v>
       </c>
@@ -15742,13 +15742,13 @@
         <v>96</v>
       </c>
       <c r="C44" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>137</v>
       </c>
       <c r="F44" t="s">
         <v>14</v>
@@ -15762,6 +15762,9 @@
       <c r="I44" t="s">
         <v>35</v>
       </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
       <c r="K44">
         <v>0</v>
       </c>
@@ -16074,11 +16077,8 @@
       <c r="DJ44">
         <v>0</v>
       </c>
-      <c r="DK44">
-        <v>0</v>
-      </c>
     </row>
-    <row r="45" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>140</v>
       </c>
@@ -16086,13 +16086,13 @@
         <v>96</v>
       </c>
       <c r="C45" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>137</v>
       </c>
       <c r="F45" t="s">
         <v>14</v>
@@ -16106,6 +16106,9 @@
       <c r="I45" t="s">
         <v>35</v>
       </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
       <c r="K45">
         <v>0</v>
       </c>
@@ -16418,11 +16421,8 @@
       <c r="DJ45">
         <v>0</v>
       </c>
-      <c r="DK45">
-        <v>0</v>
-      </c>
     </row>
-    <row r="46" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>140</v>
       </c>
@@ -16430,13 +16430,13 @@
         <v>96</v>
       </c>
       <c r="C46" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>137</v>
       </c>
       <c r="F46" t="s">
         <v>14</v>
@@ -16450,6 +16450,9 @@
       <c r="I46" t="s">
         <v>35</v>
       </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
       <c r="K46">
         <v>0</v>
       </c>
@@ -16762,11 +16765,8 @@
       <c r="DJ46">
         <v>0</v>
       </c>
-      <c r="DK46">
-        <v>0</v>
-      </c>
     </row>
-    <row r="47" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>144</v>
       </c>
@@ -16780,7 +16780,7 @@
         <v>118</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F47" t="s">
         <v>15</v>
@@ -16794,6 +16794,9 @@
       <c r="I47" t="s">
         <v>33</v>
       </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
       <c r="K47">
         <v>0</v>
       </c>
@@ -17106,11 +17109,8 @@
       <c r="DJ47">
         <v>0</v>
       </c>
-      <c r="DK47">
-        <v>0</v>
-      </c>
     </row>
-    <row r="48" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>144</v>
       </c>
@@ -17124,7 +17124,7 @@
         <v>118</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F48" t="s">
         <v>15</v>
@@ -17138,6 +17138,9 @@
       <c r="I48" t="s">
         <v>33</v>
       </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
       <c r="K48">
         <v>0</v>
       </c>
@@ -17450,11 +17453,8 @@
       <c r="DJ48">
         <v>0</v>
       </c>
-      <c r="DK48">
-        <v>0</v>
-      </c>
     </row>
-    <row r="49" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>144</v>
       </c>
@@ -17468,7 +17468,7 @@
         <v>118</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F49" t="s">
         <v>15</v>
@@ -17482,6 +17482,9 @@
       <c r="I49" t="s">
         <v>33</v>
       </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
       <c r="K49">
         <v>0</v>
       </c>
@@ -17794,11 +17797,8 @@
       <c r="DJ49">
         <v>0</v>
       </c>
-      <c r="DK49">
-        <v>0</v>
-      </c>
     </row>
-    <row r="50" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>146</v>
       </c>
@@ -17809,10 +17809,10 @@
         <v>122</v>
       </c>
       <c r="D50" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>157</v>
       </c>
       <c r="F50" t="s">
         <v>16</v>
@@ -17826,6 +17826,9 @@
       <c r="I50" t="s">
         <v>33</v>
       </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
       <c r="K50">
         <v>0</v>
       </c>
@@ -18138,11 +18141,8 @@
       <c r="DJ50">
         <v>0</v>
       </c>
-      <c r="DK50">
-        <v>0</v>
-      </c>
     </row>
-    <row r="51" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>146</v>
       </c>
@@ -18153,10 +18153,10 @@
         <v>122</v>
       </c>
       <c r="D51" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>157</v>
       </c>
       <c r="F51" t="s">
         <v>16</v>
@@ -18170,6 +18170,9 @@
       <c r="I51" t="s">
         <v>33</v>
       </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
       <c r="K51">
         <v>0</v>
       </c>
@@ -18482,11 +18485,8 @@
       <c r="DJ51">
         <v>0</v>
       </c>
-      <c r="DK51">
-        <v>0</v>
-      </c>
     </row>
-    <row r="52" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>146</v>
       </c>
@@ -18497,10 +18497,10 @@
         <v>122</v>
       </c>
       <c r="D52" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>157</v>
       </c>
       <c r="F52" t="s">
         <v>16</v>
@@ -18514,6 +18514,9 @@
       <c r="I52" t="s">
         <v>33</v>
       </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
       <c r="K52">
         <v>0</v>
       </c>
@@ -18826,11 +18829,8 @@
       <c r="DJ52">
         <v>0</v>
       </c>
-      <c r="DK52">
-        <v>0</v>
-      </c>
     </row>
-    <row r="53" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>121</v>
       </c>
@@ -18838,10 +18838,10 @@
         <v>99</v>
       </c>
       <c r="C53" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="F53" t="s">
         <v>17</v>
@@ -18855,6 +18855,9 @@
       <c r="I53" t="s">
         <v>33</v>
       </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
       <c r="K53">
         <v>0</v>
       </c>
@@ -19167,11 +19170,8 @@
       <c r="DJ53">
         <v>0</v>
       </c>
-      <c r="DK53">
-        <v>0</v>
-      </c>
     </row>
-    <row r="54" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>121</v>
       </c>
@@ -19179,10 +19179,10 @@
         <v>99</v>
       </c>
       <c r="C54" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="F54" t="s">
         <v>17</v>
@@ -19196,6 +19196,9 @@
       <c r="I54" t="s">
         <v>33</v>
       </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
       <c r="K54">
         <v>0</v>
       </c>
@@ -19508,11 +19511,8 @@
       <c r="DJ54">
         <v>0</v>
       </c>
-      <c r="DK54">
-        <v>0</v>
-      </c>
     </row>
-    <row r="55" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>121</v>
       </c>
@@ -19520,10 +19520,10 @@
         <v>99</v>
       </c>
       <c r="C55" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="F55" t="s">
         <v>17</v>
@@ -19537,6 +19537,9 @@
       <c r="I55" t="s">
         <v>33</v>
       </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
       <c r="K55">
         <v>0</v>
       </c>
@@ -19849,11 +19852,8 @@
       <c r="DJ55">
         <v>0</v>
       </c>
-      <c r="DK55">
-        <v>0</v>
-      </c>
     </row>
-    <row r="56" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>143</v>
       </c>
@@ -19861,10 +19861,10 @@
         <v>100</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F56" t="s">
         <v>18</v>
@@ -19878,6 +19878,9 @@
       <c r="I56" t="s">
         <v>33</v>
       </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
       <c r="K56">
         <v>0</v>
       </c>
@@ -20190,11 +20193,8 @@
       <c r="DJ56">
         <v>0</v>
       </c>
-      <c r="DK56">
-        <v>0</v>
-      </c>
     </row>
-    <row r="57" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>143</v>
       </c>
@@ -20202,10 +20202,10 @@
         <v>100</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F57" t="s">
         <v>18</v>
@@ -20219,6 +20219,9 @@
       <c r="I57" t="s">
         <v>33</v>
       </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
       <c r="K57">
         <v>0</v>
       </c>
@@ -20531,11 +20534,8 @@
       <c r="DJ57">
         <v>0</v>
       </c>
-      <c r="DK57">
-        <v>0</v>
-      </c>
     </row>
-    <row r="58" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>143</v>
       </c>
@@ -20543,10 +20543,10 @@
         <v>100</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F58" t="s">
         <v>18</v>
@@ -20560,6 +20560,9 @@
       <c r="I58" t="s">
         <v>33</v>
       </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
       <c r="K58">
         <v>0</v>
       </c>
@@ -20872,11 +20875,8 @@
       <c r="DJ58">
         <v>0</v>
       </c>
-      <c r="DK58">
-        <v>0</v>
-      </c>
     </row>
-    <row r="59" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>120</v>
       </c>
@@ -20884,13 +20884,13 @@
         <v>101</v>
       </c>
       <c r="C59" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="E59" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="F59" t="s">
         <v>19</v>
@@ -20904,6 +20904,9 @@
       <c r="I59" t="s">
         <v>33</v>
       </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
       <c r="K59">
         <v>0</v>
       </c>
@@ -21216,11 +21219,8 @@
       <c r="DJ59">
         <v>0</v>
       </c>
-      <c r="DK59">
-        <v>0</v>
-      </c>
     </row>
-    <row r="60" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>120</v>
       </c>
@@ -21228,13 +21228,13 @@
         <v>101</v>
       </c>
       <c r="C60" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="E60" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="F60" t="s">
         <v>19</v>
@@ -21248,6 +21248,9 @@
       <c r="I60" t="s">
         <v>33</v>
       </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
       <c r="K60">
         <v>0</v>
       </c>
@@ -21560,11 +21563,8 @@
       <c r="DJ60">
         <v>0</v>
       </c>
-      <c r="DK60">
-        <v>0</v>
-      </c>
     </row>
-    <row r="61" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>120</v>
       </c>
@@ -21572,13 +21572,13 @@
         <v>101</v>
       </c>
       <c r="C61" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="E61" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="F61" t="s">
         <v>19</v>
@@ -21592,6 +21592,9 @@
       <c r="I61" t="s">
         <v>33</v>
       </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
       <c r="K61">
         <v>0</v>
       </c>
@@ -21904,11 +21907,8 @@
       <c r="DJ61">
         <v>0</v>
       </c>
-      <c r="DK61">
-        <v>0</v>
-      </c>
     </row>
-    <row r="62" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>112</v>
       </c>
@@ -21916,10 +21916,10 @@
         <v>102</v>
       </c>
       <c r="C62" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>162</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>118</v>
@@ -21936,6 +21936,9 @@
       <c r="I62" t="s">
         <v>34</v>
       </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
       <c r="K62">
         <v>0</v>
       </c>
@@ -22248,11 +22251,8 @@
       <c r="DJ62">
         <v>0</v>
       </c>
-      <c r="DK62">
-        <v>0</v>
-      </c>
     </row>
-    <row r="63" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>112</v>
       </c>
@@ -22260,10 +22260,10 @@
         <v>102</v>
       </c>
       <c r="C63" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>162</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>118</v>
@@ -22280,6 +22280,9 @@
       <c r="I63" t="s">
         <v>34</v>
       </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
       <c r="K63">
         <v>0</v>
       </c>
@@ -22592,11 +22595,8 @@
       <c r="DJ63">
         <v>0</v>
       </c>
-      <c r="DK63">
-        <v>0</v>
-      </c>
     </row>
-    <row r="64" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>112</v>
       </c>
@@ -22604,10 +22604,10 @@
         <v>102</v>
       </c>
       <c r="C64" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>162</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>118</v>
@@ -22624,6 +22624,9 @@
       <c r="I64" t="s">
         <v>34</v>
       </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
       <c r="K64">
         <v>0</v>
       </c>
@@ -22936,11 +22939,8 @@
       <c r="DJ64">
         <v>0</v>
       </c>
-      <c r="DK64">
-        <v>0</v>
-      </c>
     </row>
-    <row r="65" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>113</v>
       </c>
@@ -22968,6 +22968,9 @@
       <c r="I65" t="s">
         <v>34</v>
       </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
       <c r="K65">
         <v>0</v>
       </c>
@@ -23280,11 +23283,8 @@
       <c r="DJ65">
         <v>0</v>
       </c>
-      <c r="DK65">
-        <v>0</v>
-      </c>
     </row>
-    <row r="66" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>113</v>
       </c>
@@ -23312,6 +23312,9 @@
       <c r="I66" t="s">
         <v>34</v>
       </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
       <c r="K66">
         <v>0</v>
       </c>
@@ -23624,11 +23627,8 @@
       <c r="DJ66">
         <v>0</v>
       </c>
-      <c r="DK66">
-        <v>0</v>
-      </c>
     </row>
-    <row r="67" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>113</v>
       </c>
@@ -23656,6 +23656,9 @@
       <c r="I67" t="s">
         <v>34</v>
       </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
       <c r="K67">
         <v>0</v>
       </c>
@@ -23968,11 +23971,8 @@
       <c r="DJ67">
         <v>0</v>
       </c>
-      <c r="DK67">
-        <v>0</v>
-      </c>
     </row>
-    <row r="68" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>158</v>
       </c>
@@ -23980,10 +23980,10 @@
         <v>104</v>
       </c>
       <c r="C68" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>155</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>118</v>
@@ -24000,6 +24000,9 @@
       <c r="I68" t="s">
         <v>34</v>
       </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
       <c r="K68">
         <v>0</v>
       </c>
@@ -24312,11 +24315,8 @@
       <c r="DJ68">
         <v>0</v>
       </c>
-      <c r="DK68">
-        <v>0</v>
-      </c>
     </row>
-    <row r="69" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>158</v>
       </c>
@@ -24324,10 +24324,10 @@
         <v>104</v>
       </c>
       <c r="C69" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>155</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>118</v>
@@ -24344,6 +24344,9 @@
       <c r="I69" t="s">
         <v>34</v>
       </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
       <c r="K69">
         <v>0</v>
       </c>
@@ -24656,11 +24659,8 @@
       <c r="DJ69">
         <v>0</v>
       </c>
-      <c r="DK69">
-        <v>0</v>
-      </c>
     </row>
-    <row r="70" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>158</v>
       </c>
@@ -24668,10 +24668,10 @@
         <v>104</v>
       </c>
       <c r="C70" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>155</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>118</v>
@@ -24688,6 +24688,9 @@
       <c r="I70" t="s">
         <v>34</v>
       </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
       <c r="K70">
         <v>0</v>
       </c>
@@ -25000,11 +25003,8 @@
       <c r="DJ70">
         <v>0</v>
       </c>
-      <c r="DK70">
-        <v>0</v>
-      </c>
     </row>
-    <row r="71" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>134</v>
       </c>
@@ -25012,10 +25012,10 @@
         <v>105</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F71" t="s">
         <v>22</v>
@@ -25029,6 +25029,9 @@
       <c r="I71" t="s">
         <v>34</v>
       </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
       <c r="K71">
         <v>0</v>
       </c>
@@ -25341,11 +25344,8 @@
       <c r="DJ71">
         <v>0</v>
       </c>
-      <c r="DK71">
-        <v>0</v>
-      </c>
     </row>
-    <row r="72" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>134</v>
       </c>
@@ -25353,10 +25353,10 @@
         <v>105</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F72" t="s">
         <v>22</v>
@@ -25370,6 +25370,9 @@
       <c r="I72" t="s">
         <v>34</v>
       </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
       <c r="K72">
         <v>0</v>
       </c>
@@ -25682,11 +25685,8 @@
       <c r="DJ72">
         <v>0</v>
       </c>
-      <c r="DK72">
-        <v>0</v>
-      </c>
     </row>
-    <row r="73" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>134</v>
       </c>
@@ -25694,10 +25694,10 @@
         <v>105</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F73" t="s">
         <v>22</v>
@@ -25711,6 +25711,9 @@
       <c r="I73" t="s">
         <v>34</v>
       </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
       <c r="K73">
         <v>0</v>
       </c>
@@ -26023,11 +26026,8 @@
       <c r="DJ73">
         <v>0</v>
       </c>
-      <c r="DK73">
-        <v>0</v>
-      </c>
     </row>
-    <row r="74" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>138</v>
       </c>
@@ -26035,13 +26035,13 @@
         <v>106</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>118</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F74" t="s">
         <v>24</v>
@@ -26055,6 +26055,9 @@
       <c r="I74" t="s">
         <v>34</v>
       </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
       <c r="K74">
         <v>0</v>
       </c>
@@ -26367,11 +26370,8 @@
       <c r="DJ74">
         <v>0</v>
       </c>
-      <c r="DK74">
-        <v>0</v>
-      </c>
     </row>
-    <row r="75" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>138</v>
       </c>
@@ -26379,13 +26379,13 @@
         <v>106</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>118</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F75" t="s">
         <v>24</v>
@@ -26399,6 +26399,9 @@
       <c r="I75" t="s">
         <v>34</v>
       </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
       <c r="K75">
         <v>0</v>
       </c>
@@ -26711,11 +26714,8 @@
       <c r="DJ75">
         <v>0</v>
       </c>
-      <c r="DK75">
-        <v>0</v>
-      </c>
     </row>
-    <row r="76" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>138</v>
       </c>
@@ -26723,13 +26723,13 @@
         <v>106</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>118</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F76" t="s">
         <v>24</v>
@@ -26743,6 +26743,9 @@
       <c r="I76" t="s">
         <v>34</v>
       </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
       <c r="K76">
         <v>0</v>
       </c>
@@ -27055,11 +27058,8 @@
       <c r="DJ76">
         <v>0</v>
       </c>
-      <c r="DK76">
-        <v>0</v>
-      </c>
     </row>
-    <row r="77" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>109</v>
       </c>
@@ -27084,6 +27084,9 @@
       <c r="I77" t="s">
         <v>35</v>
       </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
       <c r="K77">
         <v>0</v>
       </c>
@@ -27396,11 +27399,8 @@
       <c r="DJ77">
         <v>0</v>
       </c>
-      <c r="DK77">
-        <v>0</v>
-      </c>
     </row>
-    <row r="78" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>109</v>
       </c>
@@ -27425,6 +27425,9 @@
       <c r="I78" t="s">
         <v>35</v>
       </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
       <c r="K78">
         <v>0</v>
       </c>
@@ -27737,11 +27740,8 @@
       <c r="DJ78">
         <v>0</v>
       </c>
-      <c r="DK78">
-        <v>0</v>
-      </c>
     </row>
-    <row r="79" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>109</v>
       </c>
@@ -27766,6 +27766,9 @@
       <c r="I79" t="s">
         <v>35</v>
       </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
       <c r="K79">
         <v>0</v>
       </c>
@@ -28078,11 +28081,8 @@
       <c r="DJ79">
         <v>0</v>
       </c>
-      <c r="DK79">
-        <v>0</v>
-      </c>
     </row>
-    <row r="80" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>115</v>
       </c>
@@ -28092,11 +28092,11 @@
       <c r="C80" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D80" s="1">
+      <c r="D80" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E80" s="1">
         <v>380982</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>129</v>
       </c>
       <c r="F80" t="s">
         <v>26</v>
@@ -28110,6 +28110,9 @@
       <c r="I80" t="s">
         <v>35</v>
       </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
       <c r="K80">
         <v>0</v>
       </c>
@@ -28422,11 +28425,8 @@
       <c r="DJ80">
         <v>0</v>
       </c>
-      <c r="DK80">
-        <v>0</v>
-      </c>
     </row>
-    <row r="81" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>115</v>
       </c>
@@ -28436,11 +28436,11 @@
       <c r="C81" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D81" s="1">
-        <v>380982</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>129</v>
+      <c r="D81" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E81" s="1">
+        <v>380983</v>
       </c>
       <c r="F81" t="s">
         <v>26</v>
@@ -28454,6 +28454,9 @@
       <c r="I81" t="s">
         <v>35</v>
       </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
       <c r="K81">
         <v>0</v>
       </c>
@@ -28766,11 +28769,8 @@
       <c r="DJ81">
         <v>0</v>
       </c>
-      <c r="DK81">
-        <v>0</v>
-      </c>
     </row>
-    <row r="82" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>115</v>
       </c>
@@ -28780,11 +28780,11 @@
       <c r="C82" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D82" s="1">
-        <v>380982</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>129</v>
+      <c r="D82" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E82" s="1">
+        <v>380984</v>
       </c>
       <c r="F82" t="s">
         <v>26</v>
@@ -28798,6 +28798,9 @@
       <c r="I82" t="s">
         <v>35</v>
       </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
       <c r="K82">
         <v>0</v>
       </c>
@@ -29110,11 +29113,8 @@
       <c r="DJ82">
         <v>0</v>
       </c>
-      <c r="DK82">
-        <v>0</v>
-      </c>
     </row>
-    <row r="83" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>119</v>
       </c>
@@ -29122,7 +29122,7 @@
         <v>108</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>118</v>
@@ -29139,6 +29139,9 @@
       <c r="I83" t="s">
         <v>35</v>
       </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
       <c r="K83">
         <v>0</v>
       </c>
@@ -29451,11 +29454,8 @@
       <c r="DJ83">
         <v>0</v>
       </c>
-      <c r="DK83">
-        <v>0</v>
-      </c>
     </row>
-    <row r="84" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>119</v>
       </c>
@@ -29463,7 +29463,7 @@
         <v>108</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>118</v>
@@ -29480,6 +29480,9 @@
       <c r="I84" t="s">
         <v>35</v>
       </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
       <c r="K84">
         <v>0</v>
       </c>
@@ -29792,11 +29795,8 @@
       <c r="DJ84">
         <v>0</v>
       </c>
-      <c r="DK84">
-        <v>0</v>
-      </c>
     </row>
-    <row r="85" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>119</v>
       </c>
@@ -29804,7 +29804,7 @@
         <v>108</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>118</v>
@@ -29821,6 +29821,9 @@
       <c r="I85" t="s">
         <v>35</v>
       </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
       <c r="K85">
         <v>0</v>
       </c>
@@ -30133,11 +30136,8 @@
       <c r="DJ85">
         <v>0</v>
       </c>
-      <c r="DK85">
-        <v>0</v>
-      </c>
     </row>
-    <row r="86" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>135</v>
       </c>
@@ -30145,10 +30145,10 @@
         <v>109</v>
       </c>
       <c r="C86" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>146</v>
       </c>
       <c r="F86" t="s">
         <v>28</v>
@@ -30162,6 +30162,9 @@
       <c r="I86" t="s">
         <v>35</v>
       </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
       <c r="K86">
         <v>0</v>
       </c>
@@ -30474,11 +30477,8 @@
       <c r="DJ86">
         <v>0</v>
       </c>
-      <c r="DK86">
-        <v>0</v>
-      </c>
     </row>
-    <row r="87" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>135</v>
       </c>
@@ -30486,10 +30486,10 @@
         <v>109</v>
       </c>
       <c r="C87" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>146</v>
       </c>
       <c r="F87" t="s">
         <v>28</v>
@@ -30503,6 +30503,9 @@
       <c r="I87" t="s">
         <v>35</v>
       </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
       <c r="K87">
         <v>0</v>
       </c>
@@ -30815,11 +30818,8 @@
       <c r="DJ87">
         <v>0</v>
       </c>
-      <c r="DK87">
-        <v>0</v>
-      </c>
     </row>
-    <row r="88" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>135</v>
       </c>
@@ -30827,10 +30827,10 @@
         <v>109</v>
       </c>
       <c r="C88" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>146</v>
       </c>
       <c r="F88" t="s">
         <v>28</v>
@@ -30844,6 +30844,9 @@
       <c r="I88" t="s">
         <v>35</v>
       </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
       <c r="K88">
         <v>0</v>
       </c>
@@ -31156,11 +31159,8 @@
       <c r="DJ88">
         <v>0</v>
       </c>
-      <c r="DK88">
-        <v>0</v>
-      </c>
     </row>
-    <row r="89" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>137</v>
       </c>
@@ -31168,10 +31168,10 @@
         <v>110</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F89" t="s">
         <v>29</v>
@@ -31185,6 +31185,9 @@
       <c r="I89" t="s">
         <v>35</v>
       </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
       <c r="K89">
         <v>0</v>
       </c>
@@ -31497,11 +31500,8 @@
       <c r="DJ89">
         <v>0</v>
       </c>
-      <c r="DK89">
-        <v>0</v>
-      </c>
     </row>
-    <row r="90" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>137</v>
       </c>
@@ -31509,10 +31509,10 @@
         <v>110</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F90" t="s">
         <v>29</v>
@@ -31526,6 +31526,9 @@
       <c r="I90" t="s">
         <v>35</v>
       </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
       <c r="K90">
         <v>0</v>
       </c>
@@ -31838,11 +31841,8 @@
       <c r="DJ90">
         <v>0</v>
       </c>
-      <c r="DK90">
-        <v>0</v>
-      </c>
     </row>
-    <row r="91" spans="1:115" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:114" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>137</v>
       </c>
@@ -31850,10 +31850,10 @@
         <v>110</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F91" t="s">
         <v>29</v>
@@ -31867,6 +31867,9 @@
       <c r="I91" t="s">
         <v>35</v>
       </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
       <c r="K91">
         <v>0</v>
       </c>
@@ -32177,13 +32180,11 @@
         <v>0</v>
       </c>
       <c r="DJ91">
-        <v>0</v>
-      </c>
-      <c r="DK91">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/innings_blank.xlsx
+++ b/innings_blank.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jayb1/Development/innings-heatmap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB9E61E-FF7B-FA49-929B-6081B266C6F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAC23183-62AD-7F45-8388-C60E34FED2CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2200" yWindow="1560" windowWidth="27640" windowHeight="16680" xr2:uid="{4D38DE9E-45CF-F446-BA79-BBA4AB2BECC6}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$DN$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$DP$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="166">
   <si>
     <t>Baltimore Orioles</t>
   </si>
@@ -534,6 +534,12 @@
   </si>
   <si>
     <t>EFB21E</t>
+  </si>
+  <si>
+    <t>w</t>
+  </si>
+  <si>
+    <t>l</t>
   </si>
 </sst>
 </file>
@@ -912,7 +918,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B84222C-1BCC-384D-8895-C6CB4408DECD}">
-  <dimension ref="A1:DJ91"/>
+  <dimension ref="A1:DL91"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="5.1640625" bestFit="1" customWidth="1"/>
@@ -920,22 +926,23 @@
     <col min="4" max="4" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" style="1" customWidth="1"/>
     <col min="6" max="6" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="18" width="2.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="30" width="3.1640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="3" bestFit="1" customWidth="1"/>
-    <col min="32" max="42" width="3.1640625" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="2.1640625" bestFit="1" customWidth="1"/>
-    <col min="44" max="52" width="3.1640625" bestFit="1" customWidth="1"/>
-    <col min="53" max="76" width="4.1640625" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="3" bestFit="1" customWidth="1"/>
-    <col min="78" max="86" width="4.83203125" bestFit="1" customWidth="1"/>
-    <col min="87" max="110" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="111" max="112" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="113" max="113" width="8" bestFit="1" customWidth="1"/>
-    <col min="114" max="114" width="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="2.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="20" width="2.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="32" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="3" bestFit="1" customWidth="1"/>
+    <col min="34" max="44" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="2.1640625" bestFit="1" customWidth="1"/>
+    <col min="46" max="54" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="55" max="78" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="3" bestFit="1" customWidth="1"/>
+    <col min="80" max="88" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="89" max="112" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="113" max="114" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="115" max="115" width="8" bestFit="1" customWidth="1"/>
+    <col min="116" max="116" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>56</v>
       </c>
@@ -963,357 +970,363 @@
       <c r="I1" t="s">
         <v>55</v>
       </c>
-      <c r="J1">
+      <c r="J1" t="s">
+        <v>164</v>
+      </c>
+      <c r="K1" t="s">
+        <v>165</v>
+      </c>
+      <c r="L1">
         <v>1</v>
       </c>
-      <c r="K1">
+      <c r="M1">
         <v>2</v>
       </c>
-      <c r="L1">
+      <c r="N1">
         <v>3</v>
       </c>
-      <c r="M1">
+      <c r="O1">
         <v>4</v>
       </c>
-      <c r="N1">
+      <c r="P1">
         <v>5</v>
       </c>
-      <c r="O1">
+      <c r="Q1">
         <v>6</v>
       </c>
-      <c r="P1">
+      <c r="R1">
         <v>7</v>
       </c>
-      <c r="Q1">
+      <c r="S1">
         <v>8</v>
       </c>
-      <c r="R1">
+      <c r="T1">
         <v>9</v>
       </c>
-      <c r="S1">
+      <c r="U1">
         <v>10</v>
       </c>
-      <c r="T1">
+      <c r="V1">
         <v>11</v>
       </c>
-      <c r="U1">
+      <c r="W1">
         <v>12</v>
       </c>
-      <c r="V1">
+      <c r="X1">
         <v>13</v>
       </c>
-      <c r="W1">
+      <c r="Y1">
         <v>14</v>
       </c>
-      <c r="X1">
+      <c r="Z1">
         <v>15</v>
       </c>
-      <c r="Y1">
+      <c r="AA1">
         <v>16</v>
       </c>
-      <c r="Z1">
+      <c r="AB1">
         <v>17</v>
       </c>
-      <c r="AA1">
+      <c r="AC1">
         <v>18</v>
       </c>
-      <c r="AB1">
+      <c r="AD1">
         <v>19</v>
       </c>
-      <c r="AC1">
+      <c r="AE1">
         <v>20</v>
       </c>
-      <c r="AD1">
+      <c r="AF1">
         <v>21</v>
       </c>
-      <c r="AE1">
+      <c r="AG1">
         <v>22</v>
       </c>
-      <c r="AF1">
+      <c r="AH1">
         <v>23</v>
       </c>
-      <c r="AG1">
+      <c r="AI1">
         <v>24</v>
       </c>
-      <c r="AH1">
+      <c r="AJ1">
         <v>25</v>
       </c>
-      <c r="AI1">
+      <c r="AK1">
         <v>26</v>
       </c>
-      <c r="AJ1">
+      <c r="AL1">
         <v>27</v>
       </c>
-      <c r="AK1">
+      <c r="AM1">
         <v>28</v>
       </c>
-      <c r="AL1">
+      <c r="AN1">
         <v>29</v>
       </c>
-      <c r="AM1">
+      <c r="AO1">
         <v>30</v>
       </c>
-      <c r="AN1">
-        <v>31</v>
-      </c>
-      <c r="AO1">
-        <v>32</v>
-      </c>
       <c r="AP1">
+        <v>31</v>
+      </c>
+      <c r="AQ1">
+        <v>32</v>
+      </c>
+      <c r="AR1">
         <v>33</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>38</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AT1" t="s">
         <v>39</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AU1" t="s">
         <v>40</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AV1" t="s">
         <v>41</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AW1" t="s">
         <v>42</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AX1" t="s">
         <v>43</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AY1" t="s">
         <v>44</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AZ1" t="s">
         <v>45</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BA1" t="s">
         <v>46</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BB1" t="s">
         <v>47</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BC1" t="s">
         <v>57</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BD1" t="s">
         <v>58</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BE1" t="s">
         <v>59</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BF1" t="s">
         <v>60</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BG1" t="s">
         <v>61</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BH1" t="s">
         <v>62</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BI1" t="s">
         <v>63</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BJ1" t="s">
         <v>64</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BK1" t="s">
         <v>65</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BL1" t="s">
         <v>66</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BM1" t="s">
         <v>67</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BN1" t="s">
         <v>68</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BO1" t="s">
         <v>69</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BP1" t="s">
         <v>70</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BQ1" t="s">
         <v>71</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BR1" t="s">
         <v>72</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BS1" t="s">
         <v>73</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BT1" t="s">
         <v>74</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BU1" t="s">
         <v>75</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BV1" t="s">
         <v>76</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BW1" t="s">
         <v>77</v>
       </c>
-      <c r="BV1" t="s">
+      <c r="BX1" t="s">
         <v>78</v>
       </c>
-      <c r="BW1" t="s">
+      <c r="BY1" t="s">
         <v>79</v>
       </c>
-      <c r="BX1" t="s">
+      <c r="BZ1" t="s">
         <v>80</v>
       </c>
-      <c r="BY1" t="s">
+      <c r="CA1" t="s">
         <v>48</v>
       </c>
-      <c r="BZ1" t="str">
-        <f>_xlfn.CONCAT(J1,"avg")</f>
+      <c r="CB1" t="str">
+        <f>_xlfn.CONCAT(L1,"avg")</f>
         <v>1avg</v>
       </c>
-      <c r="CA1" t="str">
-        <f t="shared" ref="CA1:CV1" si="0">_xlfn.CONCAT(K1,"avg")</f>
+      <c r="CC1" t="str">
+        <f t="shared" ref="CC1:CX1" si="0">_xlfn.CONCAT(M1,"avg")</f>
         <v>2avg</v>
       </c>
-      <c r="CB1" t="str">
+      <c r="CD1" t="str">
         <f t="shared" si="0"/>
         <v>3avg</v>
       </c>
-      <c r="CC1" t="str">
+      <c r="CE1" t="str">
         <f t="shared" si="0"/>
         <v>4avg</v>
       </c>
-      <c r="CD1" t="str">
+      <c r="CF1" t="str">
         <f t="shared" si="0"/>
         <v>5avg</v>
       </c>
-      <c r="CE1" t="str">
+      <c r="CG1" t="str">
         <f t="shared" si="0"/>
         <v>6avg</v>
       </c>
-      <c r="CF1" t="str">
+      <c r="CH1" t="str">
         <f t="shared" si="0"/>
         <v>7avg</v>
       </c>
-      <c r="CG1" t="str">
+      <c r="CI1" t="str">
         <f t="shared" si="0"/>
         <v>8avg</v>
       </c>
-      <c r="CH1" t="str">
+      <c r="CJ1" t="str">
         <f t="shared" si="0"/>
         <v>9avg</v>
       </c>
-      <c r="CI1" t="str">
+      <c r="CK1" t="str">
         <f t="shared" si="0"/>
         <v>10avg</v>
       </c>
-      <c r="CJ1" t="str">
+      <c r="CL1" t="str">
         <f t="shared" si="0"/>
         <v>11avg</v>
       </c>
-      <c r="CK1" t="str">
+      <c r="CM1" t="str">
         <f t="shared" si="0"/>
         <v>12avg</v>
       </c>
-      <c r="CL1" t="str">
+      <c r="CN1" t="str">
         <f t="shared" si="0"/>
         <v>13avg</v>
       </c>
-      <c r="CM1" t="str">
+      <c r="CO1" t="str">
         <f t="shared" si="0"/>
         <v>14avg</v>
       </c>
-      <c r="CN1" t="str">
+      <c r="CP1" t="str">
         <f t="shared" si="0"/>
         <v>15avg</v>
       </c>
-      <c r="CO1" t="str">
+      <c r="CQ1" t="str">
         <f t="shared" si="0"/>
         <v>16avg</v>
       </c>
-      <c r="CP1" t="str">
+      <c r="CR1" t="str">
         <f t="shared" si="0"/>
         <v>17avg</v>
       </c>
-      <c r="CQ1" t="str">
+      <c r="CS1" t="str">
         <f t="shared" si="0"/>
         <v>18avg</v>
       </c>
-      <c r="CR1" t="str">
+      <c r="CT1" t="str">
         <f t="shared" si="0"/>
         <v>19avg</v>
       </c>
-      <c r="CS1" t="str">
+      <c r="CU1" t="str">
         <f t="shared" si="0"/>
         <v>20avg</v>
       </c>
-      <c r="CT1" t="str">
+      <c r="CV1" t="str">
         <f t="shared" si="0"/>
         <v>21avg</v>
       </c>
-      <c r="CU1" t="str">
+      <c r="CW1" t="str">
         <f t="shared" si="0"/>
         <v>22avg</v>
       </c>
-      <c r="CV1" t="str">
+      <c r="CX1" t="str">
         <f t="shared" si="0"/>
         <v>23avg</v>
       </c>
-      <c r="CW1" t="str">
-        <f>_xlfn.CONCAT(AG1,"avg")</f>
+      <c r="CY1" t="str">
+        <f>_xlfn.CONCAT(AI1,"avg")</f>
         <v>24avg</v>
       </c>
-      <c r="CX1" t="str">
-        <f t="shared" ref="CX1" si="1">_xlfn.CONCAT(AH1,"avg")</f>
+      <c r="CZ1" t="str">
+        <f t="shared" ref="CZ1" si="1">_xlfn.CONCAT(AJ1,"avg")</f>
         <v>25avg</v>
       </c>
-      <c r="CY1" t="str">
-        <f t="shared" ref="CY1" si="2">_xlfn.CONCAT(AI1,"avg")</f>
+      <c r="DA1" t="str">
+        <f t="shared" ref="DA1" si="2">_xlfn.CONCAT(AK1,"avg")</f>
         <v>26avg</v>
       </c>
-      <c r="CZ1" t="str">
-        <f t="shared" ref="CZ1" si="3">_xlfn.CONCAT(AJ1,"avg")</f>
+      <c r="DB1" t="str">
+        <f t="shared" ref="DB1" si="3">_xlfn.CONCAT(AL1,"avg")</f>
         <v>27avg</v>
       </c>
-      <c r="DA1" t="str">
-        <f t="shared" ref="DA1" si="4">_xlfn.CONCAT(AK1,"avg")</f>
+      <c r="DC1" t="str">
+        <f t="shared" ref="DC1" si="4">_xlfn.CONCAT(AM1,"avg")</f>
         <v>28avg</v>
       </c>
-      <c r="DB1" t="str">
-        <f t="shared" ref="DB1" si="5">_xlfn.CONCAT(AL1,"avg")</f>
+      <c r="DD1" t="str">
+        <f t="shared" ref="DD1" si="5">_xlfn.CONCAT(AN1,"avg")</f>
         <v>29avg</v>
       </c>
-      <c r="DC1" t="str">
-        <f t="shared" ref="DC1" si="6">_xlfn.CONCAT(AM1,"avg")</f>
+      <c r="DE1" t="str">
+        <f t="shared" ref="DE1" si="6">_xlfn.CONCAT(AO1,"avg")</f>
         <v>30avg</v>
       </c>
-      <c r="DD1" t="str">
-        <f t="shared" ref="DD1" si="7">_xlfn.CONCAT(AN1,"avg")</f>
+      <c r="DF1" t="str">
+        <f t="shared" ref="DF1" si="7">_xlfn.CONCAT(AP1,"avg")</f>
         <v>31avg</v>
       </c>
-      <c r="DE1" t="str">
-        <f t="shared" ref="DE1" si="8">_xlfn.CONCAT(AO1,"avg")</f>
+      <c r="DG1" t="str">
+        <f t="shared" ref="DG1" si="8">_xlfn.CONCAT(AQ1,"avg")</f>
         <v>32avg</v>
       </c>
-      <c r="DF1" t="str">
-        <f t="shared" ref="DF1" si="9">_xlfn.CONCAT(AP1,"avg")</f>
+      <c r="DH1" t="str">
+        <f t="shared" ref="DH1" si="9">_xlfn.CONCAT(AR1,"avg")</f>
         <v>33avg</v>
       </c>
-      <c r="DG1" t="str">
-        <f t="shared" ref="DG1" si="10">_xlfn.CONCAT(AQ1,"avg")</f>
+      <c r="DI1" t="str">
+        <f t="shared" ref="DI1" si="10">_xlfn.CONCAT(AS1,"avg")</f>
         <v>xavg</v>
       </c>
-      <c r="DH1" t="s">
+      <c r="DJ1" t="s">
         <v>49</v>
       </c>
-      <c r="DI1" t="s">
+      <c r="DK1" t="s">
         <v>50</v>
       </c>
-      <c r="DJ1" t="s">
+      <c r="DL1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>110</v>
       </c>
@@ -1341,8 +1354,14 @@
       <c r="I2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="3" spans="1:114" x14ac:dyDescent="0.2">
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>110</v>
       </c>
@@ -1370,8 +1389,14 @@
       <c r="I3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="4" spans="1:114" x14ac:dyDescent="0.2">
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>110</v>
       </c>
@@ -1399,8 +1424,14 @@
       <c r="I4" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="5" spans="1:114" x14ac:dyDescent="0.2">
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>111</v>
       </c>
@@ -1428,8 +1459,14 @@
       <c r="I5" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="6" spans="1:114" x14ac:dyDescent="0.2">
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>111</v>
       </c>
@@ -1457,8 +1494,14 @@
       <c r="I6" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="7" spans="1:114" x14ac:dyDescent="0.2">
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>111</v>
       </c>
@@ -1486,8 +1529,14 @@
       <c r="I7" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="8" spans="1:114" x14ac:dyDescent="0.2">
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>147</v>
       </c>
@@ -1512,8 +1561,14 @@
       <c r="I8" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="9" spans="1:114" x14ac:dyDescent="0.2">
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>147</v>
       </c>
@@ -1538,8 +1593,14 @@
       <c r="I9" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="10" spans="1:114" x14ac:dyDescent="0.2">
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>147</v>
       </c>
@@ -1564,8 +1625,14 @@
       <c r="I10" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="11" spans="1:114" x14ac:dyDescent="0.2">
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>139</v>
       </c>
@@ -1593,8 +1660,14 @@
       <c r="I11" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="12" spans="1:114" x14ac:dyDescent="0.2">
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>139</v>
       </c>
@@ -1622,8 +1695,14 @@
       <c r="I12" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="13" spans="1:114" x14ac:dyDescent="0.2">
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>139</v>
       </c>
@@ -1651,8 +1730,14 @@
       <c r="I13" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="14" spans="1:114" x14ac:dyDescent="0.2">
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>141</v>
       </c>
@@ -1680,8 +1765,14 @@
       <c r="I14" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="15" spans="1:114" x14ac:dyDescent="0.2">
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>141</v>
       </c>
@@ -1709,8 +1800,14 @@
       <c r="I15" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="16" spans="1:114" x14ac:dyDescent="0.2">
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>141</v>
       </c>
@@ -1738,8 +1835,14 @@
       <c r="I16" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>145</v>
       </c>
@@ -1764,8 +1867,14 @@
       <c r="I17" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>145</v>
       </c>
@@ -1790,8 +1899,14 @@
       <c r="I18" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>145</v>
       </c>
@@ -1816,8 +1931,14 @@
       <c r="I19" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>114</v>
       </c>
@@ -1845,8 +1966,14 @@
       <c r="I20" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>114</v>
       </c>
@@ -1874,8 +2001,14 @@
       <c r="I21" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>114</v>
       </c>
@@ -1903,8 +2036,14 @@
       <c r="I22" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>116</v>
       </c>
@@ -1932,8 +2071,14 @@
       <c r="I23" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>116</v>
       </c>
@@ -1961,8 +2106,14 @@
       <c r="I24" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>116</v>
       </c>
@@ -1990,8 +2141,14 @@
       <c r="I25" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>118</v>
       </c>
@@ -2016,8 +2173,14 @@
       <c r="I26" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>118</v>
       </c>
@@ -2042,8 +2205,14 @@
       <c r="I27" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>118</v>
       </c>
@@ -2068,8 +2237,14 @@
       <c r="I28" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>142</v>
       </c>
@@ -2097,8 +2272,14 @@
       <c r="I29" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>142</v>
       </c>
@@ -2126,8 +2307,14 @@
       <c r="I30" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>142</v>
       </c>
@@ -2155,8 +2342,14 @@
       <c r="I31" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>133</v>
       </c>
@@ -2184,8 +2377,14 @@
       <c r="I32" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>133</v>
       </c>
@@ -2213,8 +2412,14 @@
       <c r="I33" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>133</v>
       </c>
@@ -2242,8 +2447,14 @@
       <c r="I34" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>117</v>
       </c>
@@ -2271,8 +2482,14 @@
       <c r="I35" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>117</v>
       </c>
@@ -2300,8 +2517,14 @@
       <c r="I36" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>117</v>
       </c>
@@ -2329,8 +2552,14 @@
       <c r="I37" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>108</v>
       </c>
@@ -2358,8 +2587,14 @@
       <c r="I38" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>108</v>
       </c>
@@ -2387,8 +2622,14 @@
       <c r="I39" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>108</v>
       </c>
@@ -2416,8 +2657,14 @@
       <c r="I40" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>136</v>
       </c>
@@ -2445,8 +2692,14 @@
       <c r="I41" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>136</v>
       </c>
@@ -2474,8 +2727,14 @@
       <c r="I42" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>136</v>
       </c>
@@ -2503,8 +2762,14 @@
       <c r="I43" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>140</v>
       </c>
@@ -2532,8 +2797,14 @@
       <c r="I44" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>140</v>
       </c>
@@ -2561,8 +2832,14 @@
       <c r="I45" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>140</v>
       </c>
@@ -2590,8 +2867,14 @@
       <c r="I46" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>144</v>
       </c>
@@ -2619,8 +2902,14 @@
       <c r="I47" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>144</v>
       </c>
@@ -2648,8 +2937,14 @@
       <c r="I48" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>144</v>
       </c>
@@ -2677,8 +2972,14 @@
       <c r="I49" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>146</v>
       </c>
@@ -2706,8 +3007,14 @@
       <c r="I50" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>146</v>
       </c>
@@ -2735,8 +3042,14 @@
       <c r="I51" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>146</v>
       </c>
@@ -2764,8 +3077,14 @@
       <c r="I52" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>121</v>
       </c>
@@ -2790,8 +3109,14 @@
       <c r="I53" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>121</v>
       </c>
@@ -2816,8 +3141,14 @@
       <c r="I54" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>121</v>
       </c>
@@ -2842,8 +3173,14 @@
       <c r="I55" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>143</v>
       </c>
@@ -2868,8 +3205,14 @@
       <c r="I56" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>143</v>
       </c>
@@ -2894,8 +3237,14 @@
       <c r="I57" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>143</v>
       </c>
@@ -2920,8 +3269,14 @@
       <c r="I58" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>120</v>
       </c>
@@ -2949,8 +3304,14 @@
       <c r="I59" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>120</v>
       </c>
@@ -2978,8 +3339,14 @@
       <c r="I60" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>120</v>
       </c>
@@ -3007,8 +3374,14 @@
       <c r="I61" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>112</v>
       </c>
@@ -3036,8 +3409,14 @@
       <c r="I62" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>112</v>
       </c>
@@ -3065,8 +3444,14 @@
       <c r="I63" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>112</v>
       </c>
@@ -3094,8 +3479,14 @@
       <c r="I64" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>113</v>
       </c>
@@ -3123,8 +3514,14 @@
       <c r="I65" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>113</v>
       </c>
@@ -3152,8 +3549,14 @@
       <c r="I66" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>113</v>
       </c>
@@ -3181,8 +3584,14 @@
       <c r="I67" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>158</v>
       </c>
@@ -3210,8 +3619,14 @@
       <c r="I68" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>158</v>
       </c>
@@ -3239,8 +3654,14 @@
       <c r="I69" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>158</v>
       </c>
@@ -3268,8 +3689,14 @@
       <c r="I70" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>134</v>
       </c>
@@ -3294,8 +3721,14 @@
       <c r="I71" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>134</v>
       </c>
@@ -3320,8 +3753,14 @@
       <c r="I72" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>134</v>
       </c>
@@ -3346,8 +3785,14 @@
       <c r="I73" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>138</v>
       </c>
@@ -3375,8 +3820,14 @@
       <c r="I74" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>138</v>
       </c>
@@ -3404,8 +3855,14 @@
       <c r="I75" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>138</v>
       </c>
@@ -3433,8 +3890,14 @@
       <c r="I76" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>109</v>
       </c>
@@ -3459,8 +3922,14 @@
       <c r="I77" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>109</v>
       </c>
@@ -3485,8 +3954,14 @@
       <c r="I78" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>109</v>
       </c>
@@ -3511,8 +3986,14 @@
       <c r="I79" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>115</v>
       </c>
@@ -3540,8 +4021,14 @@
       <c r="I80" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>115</v>
       </c>
@@ -3569,8 +4056,14 @@
       <c r="I81" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>115</v>
       </c>
@@ -3598,8 +4091,14 @@
       <c r="I82" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>119</v>
       </c>
@@ -3624,8 +4123,14 @@
       <c r="I83" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>119</v>
       </c>
@@ -3650,8 +4155,14 @@
       <c r="I84" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>119</v>
       </c>
@@ -3676,8 +4187,14 @@
       <c r="I85" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>135</v>
       </c>
@@ -3702,8 +4219,14 @@
       <c r="I86" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>135</v>
       </c>
@@ -3728,8 +4251,14 @@
       <c r="I87" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>135</v>
       </c>
@@ -3754,8 +4283,14 @@
       <c r="I88" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>137</v>
       </c>
@@ -3780,8 +4315,14 @@
       <c r="I89" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>137</v>
       </c>
@@ -3806,8 +4347,14 @@
       <c r="I90" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>137</v>
       </c>
@@ -3831,6 +4378,12 @@
       </c>
       <c r="I91" t="s">
         <v>35</v>
+      </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
+      <c r="K91">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
